--- a/dataset/C2019-06 Production Line Change.xlsx
+++ b/dataset/C2019-06 Production Line Change.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="20910"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/jisantos_ubu_es/Documents/CodeDrive/GitHub/counterEVM-1/dataset/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_191DC62CBD9728986555525563FA92537621357E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5B79789-C849-419F-83CE-8B7F0C961DDC}"/>
   <bookViews>
-    <workbookView xWindow="32960" yWindow="0" windowWidth="25600" windowHeight="14420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline Schedule" sheetId="1" r:id="rId1"/>
     <sheet name="Gantt chart" sheetId="2" r:id="rId2"/>
     <sheet name="Resources" sheetId="3" r:id="rId3"/>
     <sheet name="Risk Analysis" sheetId="4" r:id="rId4"/>
-    <sheet name="Project Control - TP1" sheetId="5" r:id="rId5"/>
+    <sheet name="TP1" sheetId="5" r:id="rId5"/>
     <sheet name="TP2" sheetId="6" r:id="rId6"/>
     <sheet name="TP3" sheetId="7" r:id="rId7"/>
     <sheet name="TP4" sheetId="8" r:id="rId8"/>
@@ -1048,10 +1054,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\€"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00\€"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1307,7 +1312,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1321,25 +1326,25 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1348,7 +1353,7 @@
     <xf numFmtId="9" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1374,10 +1379,10 @@
     <xf numFmtId="49" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1389,16 +1394,13 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -1508,13 +1510,21 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1647,86 +1657,91 @@
             <c:numRef>
               <c:f>'Baseline Schedule'!$F$4:$F$28</c:f>
               <c:numCache>
-                <c:formatCode>dd/mm/yyyy\ h:mm</c:formatCode>
+                <c:formatCode>m/d/yyyy\ h:mm</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>42674.3333333333</c:v>
+                  <c:v>42674.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42793.3333333333</c:v>
+                  <c:v>42793.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>42793.3333333333</c:v>
+                  <c:v>42793.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>42793.3333333333</c:v>
+                  <c:v>42793.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>42922.3333333333</c:v>
+                  <c:v>42922.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>42922.3333333333</c:v>
+                  <c:v>42922.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>42922.3333333333</c:v>
+                  <c:v>42922.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>42821.3333333333</c:v>
+                  <c:v>42821.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>42821.3333333333</c:v>
+                  <c:v>42821.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>42950.3333333333</c:v>
+                  <c:v>42950.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>42950.3333333333</c:v>
+                  <c:v>42950.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>42944.3333333333</c:v>
+                  <c:v>42944.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>43031.3333333333</c:v>
+                  <c:v>43031.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>43031.3333333333</c:v>
+                  <c:v>43031.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>42968.3333333333</c:v>
+                  <c:v>42968.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>42968.3333333333</c:v>
+                  <c:v>42968.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>43003.3333333333</c:v>
+                  <c:v>43003.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>43003.3333333333</c:v>
+                  <c:v>43003.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>43003.3333333333</c:v>
+                  <c:v>43003.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>43003.3333333333</c:v>
+                  <c:v>43003.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>43059.3333333333</c:v>
+                  <c:v>43059.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>43045.3333333333</c:v>
+                  <c:v>43045.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>43119.3333333333</c:v>
+                  <c:v>43119.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>43070.3333333333</c:v>
+                  <c:v>43070.333333333299</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>43332.3333333333</c:v>
+                  <c:v>43332.333333333299</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DA6D-47C9-AA63-6BA0889E91CC}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1744,6 +1759,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1754,6 +1774,11 @@
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1764,6 +1789,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1774,6 +1804,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1784,6 +1819,11 @@
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1794,6 +1834,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000C-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1804,6 +1849,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000E-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1814,6 +1864,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000010-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1824,6 +1879,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000012-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1834,6 +1894,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000014-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1844,6 +1909,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000016-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -1854,6 +1924,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000018-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -1864,6 +1939,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001A-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
@@ -1874,6 +1954,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001C-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
@@ -1884,6 +1969,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001E-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
@@ -1894,6 +1984,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000020-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
@@ -1904,6 +1999,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000022-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
@@ -1914,6 +2014,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000024-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="18"/>
@@ -1924,6 +2029,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000026-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="19"/>
@@ -1934,6 +2044,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000028-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="20"/>
@@ -1944,6 +2059,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002A-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
@@ -1954,6 +2074,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002C-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="22"/>
@@ -1964,6 +2089,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002E-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="23"/>
@@ -1974,6 +2104,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000030-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="24"/>
@@ -1984,6 +2119,11 @@
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000032-DA6D-47C9-AA63-6BA0889E91CC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2152,6 +2292,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000033-DA6D-47C9-AA63-6BA0889E91CC}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2204,8 +2349,8 @@
         <c:axId val="2095065960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="43343.70833333334"/>
-          <c:min val="42674.33333333334"/>
+          <c:max val="43343.708333333343"/>
+          <c:min val="42674.333333333343"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="t"/>
@@ -2250,9 +2395,9 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2341,45 +2486,50 @@
             <c:numRef>
               <c:f>'Tracking Overview'!$F$3:$F$13</c:f>
               <c:numCache>
-                <c:formatCode>###0.00\€</c:formatCode>
+                <c:formatCode>#,##0.00\€</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>7116.91729323308</c:v>
+                  <c:v>7116.9172932330803</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17210.0</c:v>
+                  <c:v>17210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>119086.965986395</c:v>
+                  <c:v>119086.96598639499</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>236467.069257651</c:v>
+                  <c:v>236467.06925765099</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>516473.0</c:v>
+                  <c:v>516473</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>790691.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.12979E6</c:v>
+                  <c:v>1129790</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.26257E6</c:v>
+                  <c:v>1262570</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.35297E6</c:v>
+                  <c:v>1352970</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.39457E6</c:v>
+                  <c:v>1394570</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.53406E6</c:v>
+                  <c:v>1534060</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-18CE-46FA-AEA8-7D8ADCE8EDE6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2435,45 +2585,50 @@
             <c:numRef>
               <c:f>'Tracking Overview'!$E$3:$E$13</c:f>
               <c:numCache>
-                <c:formatCode>###0.00\€</c:formatCode>
+                <c:formatCode>#,##0.00\€</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>6492.48120300751</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15700.0</c:v>
+                  <c:v>15700</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>118037.414965986</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>233457.640580324</c:v>
+                  <c:v>233457.64058032399</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>516610.0</c:v>
+                  <c:v>516610</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>788950.0</c:v>
+                  <c:v>788950</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.12643E6</c:v>
+                  <c:v>1126430</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.25725E6</c:v>
+                  <c:v>1257250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.3385E6</c:v>
+                  <c:v>1338500</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.37365E6</c:v>
+                  <c:v>1373650</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.512E6</c:v>
+                  <c:v>1512000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-18CE-46FA-AEA8-7D8ADCE8EDE6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -2529,45 +2684,50 @@
             <c:numRef>
               <c:f>'Tracking Overview'!$D$3:$D$13</c:f>
               <c:numCache>
-                <c:formatCode>###0.00\€</c:formatCode>
+                <c:formatCode>#,##0.00\€</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>8092.78350515464</c:v>
+                  <c:v>8092.7835051546399</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>28054.9828178694</c:v>
+                  <c:v>28054.982817869401</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>146813.193565498</c:v>
+                  <c:v>146813.19356549799</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>294932.968193346</c:v>
+                  <c:v>294932.96819334599</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>440829.708240078</c:v>
+                  <c:v>440829.70824007801</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>686858.435606356</c:v>
+                  <c:v>686858.43560635601</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.13896975280904E6</c:v>
+                  <c:v>1138969.75280904</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.29296953847733E6</c:v>
+                  <c:v>1292969.53847733</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.31856420346639E6</c:v>
+                  <c:v>1318564.20346639</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.512E6</c:v>
+                  <c:v>1512000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.512E6</c:v>
+                  <c:v>1512000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-18CE-46FA-AEA8-7D8ADCE8EDE6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2577,7 +2737,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="2107698456"/>
         <c:axId val="2107703880"/>
@@ -2604,6 +2763,7 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2637,7 +2797,7 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
-        <c:numFmt formatCode="###0.00\€" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0.00\€" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2663,9 +2823,9 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2760,39 +2920,44 @@
                   <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.557692307692308</c:v>
+                  <c:v>0.55769230769230804</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.835365853658537</c:v>
+                  <c:v>0.83536585365853699</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.91</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.05288461538462</c:v>
+                  <c:v>1.0528846153846201</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1.04871323529412</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.992690058479532</c:v>
+                  <c:v>0.99269005847953196</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.948397435897436</c:v>
+                  <c:v>0.94839743589743597</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1.03992628992629</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.946875</c:v>
+                  <c:v>0.94687500000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.958083832335329</c:v>
+                  <c:v>0.95808383233532901</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6B59-42D5-B37A-3F75467CA897}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2854,39 +3019,44 @@
                   <c:v>0.802255639097744</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.559615384615385</c:v>
+                  <c:v>0.55961538461538496</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.803997325440144</c:v>
+                  <c:v>0.80399732544014402</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.791561696240342</c:v>
+                  <c:v>0.79156169624034201</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.17190377677235</c:v>
+                  <c:v>1.1719037767723499</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.14863552531537</c:v>
+                  <c:v>1.1486355253153699</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.988990267056595</c:v>
+                  <c:v>0.98899026705659498</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.97237402938402</c:v>
+                  <c:v>0.97237402938401996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.01511932182081</c:v>
+                  <c:v>1.0151193218208101</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.908498677248677</c:v>
+                  <c:v>0.90849867724867694</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6B59-42D5-B37A-3F75467CA897}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -2945,42 +3115,47 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1.0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.822571434824158</c:v>
+                  <c:v>0.82257143482415795</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.902787179991821</c:v>
+                  <c:v>0.90278717999182101</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.871510171982249</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.938010123835544</c:v>
+                  <c:v>0.93801012383554405</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.917643833315406</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.982831758630992</c:v>
+                  <c:v>0.98283175863099204</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.970937167625606</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.990280995514953</c:v>
+                  <c:v>0.99028099551495297</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6B59-42D5-B37A-3F75467CA897}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2990,7 +3165,6 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="2109973432"/>
         <c:axId val="2109978856"/>
@@ -3017,6 +3191,7 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3092,7 +3267,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3127,7 +3308,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3162,7 +3349,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3464,23 +3657,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
-    <col min="4" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="25.6640625" customWidth="1"/>
-    <col min="10" max="12" width="10.6640625" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.6328125" customWidth="1"/>
+    <col min="2" max="2" width="25.6328125" customWidth="1"/>
+    <col min="3" max="3" width="5.6328125" customWidth="1"/>
+    <col min="4" max="5" width="16.6328125" customWidth="1"/>
+    <col min="6" max="7" width="13.6328125" customWidth="1"/>
+    <col min="8" max="8" width="8.6328125" customWidth="1"/>
+    <col min="9" max="9" width="25.6328125" customWidth="1"/>
+    <col min="10" max="12" width="10.6328125" customWidth="1"/>
+    <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -3506,54 +3699,54 @@
       <c r="M1" s="30"/>
       <c r="N1" s="30"/>
     </row>
-    <row r="2" spans="1:17" ht="30" customHeight="1">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -3588,7 +3781,7 @@
         <v>669.375</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3631,7 +3824,7 @@
         <v>406.375</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>26</v>
       </c>
@@ -3666,7 +3859,7 @@
         <v>28.375</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="23">
+    <row r="6" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -3709,7 +3902,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="23">
+    <row r="7" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -3754,7 +3947,7 @@
         <v>28.375</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>27</v>
       </c>
@@ -3789,7 +3982,7 @@
         <v>28.375</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="23">
+    <row r="9" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -3834,7 +4027,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="23">
+    <row r="10" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -3879,7 +4072,7 @@
         <v>28.375</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -3924,7 +4117,7 @@
         <v>210.375</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -3969,7 +4162,7 @@
         <v>217.375</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -4014,7 +4207,7 @@
         <v>162.375</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -4059,7 +4252,7 @@
         <v>169.375</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="23">
+    <row r="15" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -4104,7 +4297,7 @@
         <v>388.375</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -4149,7 +4342,7 @@
         <v>137.375</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="23">
+    <row r="17" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -4194,7 +4387,7 @@
         <v>137.375</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -4239,7 +4432,7 @@
         <v>214.375</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -4284,7 +4477,7 @@
         <v>211.375</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -4329,7 +4522,7 @@
         <v>176.375</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -4374,7 +4567,7 @@
         <v>294.375</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -4419,7 +4612,7 @@
         <v>144.375</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -4464,7 +4657,7 @@
         <v>144.375</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="23">
+    <row r="24" spans="1:17" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>19</v>
       </c>
@@ -4509,7 +4702,7 @@
         <v>179.375</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>20</v>
       </c>
@@ -4554,7 +4747,7 @@
         <v>25.375</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>21</v>
       </c>
@@ -4567,7 +4760,7 @@
       <c r="D26" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E26" s="34" t="s">
+      <c r="E26" s="29" t="s">
         <v>324</v>
       </c>
       <c r="F26" s="8">
@@ -4599,7 +4792,7 @@
         <v>88.375</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>22</v>
       </c>
@@ -4612,7 +4805,7 @@
       <c r="D27" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="E27" s="34" t="s">
+      <c r="E27" s="29" t="s">
         <v>324</v>
       </c>
       <c r="F27" s="8">
@@ -4644,7 +4837,7 @@
         <v>28.375</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="34">
+    <row r="28" spans="1:17" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>23</v>
       </c>
@@ -4706,24 +4899,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -4737,7 +4930,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -4773,7 +4966,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -4847,7 +5040,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -4897,7 +5090,7 @@
         <v>686858.43560635601</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -4969,7 +5162,7 @@
         <v>146749.14089347099</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -5019,7 +5212,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -5091,7 +5284,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -5163,7 +5356,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -5213,7 +5406,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -5285,7 +5478,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -5357,7 +5550,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -5429,7 +5622,7 @@
         <v>58000</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -5501,7 +5694,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -5573,7 +5766,7 @@
         <v>34786.324786324803</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -5645,7 +5838,7 @@
         <v>12131.1475409836</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -5717,7 +5910,7 @@
         <v>63357.400722021703</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -5789,7 +5982,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -5861,7 +6054,7 @@
         <v>5950</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -5933,7 +6126,7 @@
         <v>138000</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -6005,7 +6198,7 @@
         <v>18355.2631578947</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -6077,7 +6270,7 @@
         <v>2622.04724409449</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -6149,7 +6342,7 @@
         <v>15606.635071090001</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -6221,7 +6414,7 @@
         <v>17619.0476190476</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -6293,7 +6486,7 @@
         <v>10571.4285714286</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -6365,7 +6558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -6437,7 +6630,7 @@
         <v>8750</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -6507,7 +6700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -6577,7 +6770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -6665,24 +6858,24 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -6696,7 +6889,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -6732,7 +6925,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -6806,7 +6999,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -6856,7 +7049,7 @@
         <v>1138969.75280904</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -6928,7 +7121,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -6978,7 +7171,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -7050,7 +7243,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -7122,7 +7315,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -7172,7 +7365,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -7244,7 +7437,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -7316,7 +7509,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -7388,7 +7581,7 @@
         <v>58000</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -7460,7 +7653,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -7532,7 +7725,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -7604,7 +7797,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -7676,7 +7869,7 @@
         <v>120216.606498195</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -7748,7 +7941,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -7820,7 +8013,7 @@
         <v>30450</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -7892,7 +8085,7 @@
         <v>293806.45161290298</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -7964,7 +8157,7 @@
         <v>39078.947368421002</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -8036,7 +8229,7 @@
         <v>7582.6771653543301</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -8108,7 +8301,7 @@
         <v>45132.701421800899</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -8180,7 +8373,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -8252,7 +8445,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -8324,7 +8517,7 @@
         <v>20615.384615384599</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -8396,7 +8589,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -8466,7 +8659,7 @@
         <v>9126.9841269841309</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -8538,7 +8731,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -8626,24 +8819,24 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -8657,7 +8850,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -8693,7 +8886,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -8767,7 +8960,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -8817,7 +9010,7 @@
         <v>1292969.53847733</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -8889,7 +9082,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -8939,7 +9132,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -9011,7 +9204,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -9083,7 +9276,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -9133,7 +9326,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -9205,7 +9398,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -9277,7 +9470,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -9349,7 +9542,7 @@
         <v>58000</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -9421,7 +9614,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -9493,7 +9686,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -9565,7 +9758,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -9637,7 +9830,7 @@
         <v>159205.776173285</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -9709,7 +9902,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -9781,7 +9974,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -9853,7 +10046,7 @@
         <v>345000</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -9925,7 +10118,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -9997,7 +10190,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -10069,7 +10262,7 @@
         <v>65379.146919431303</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -10141,7 +10334,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -10213,7 +10406,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -10285,7 +10478,7 @@
         <v>35384.615384615397</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -10357,7 +10550,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -10429,7 +10622,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -10501,7 +10694,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -10589,24 +10782,24 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -10620,7 +10813,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -10656,7 +10849,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -10730,7 +10923,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -10780,7 +10973,7 @@
         <v>1318564.20346639</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -10852,7 +11045,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -10902,7 +11095,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -10974,7 +11167,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -11046,7 +11239,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -11096,7 +11289,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -11168,7 +11361,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -11240,7 +11433,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -11312,7 +11505,7 @@
         <v>58000</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -11384,7 +11577,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -11456,7 +11649,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -11528,7 +11721,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -11600,7 +11793,7 @@
         <v>173014.44043321299</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -11672,7 +11865,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -11744,7 +11937,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -11816,7 +12009,7 @@
         <v>345000</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -11888,7 +12081,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -11960,7 +12153,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -12032,7 +12225,7 @@
         <v>72549.763033175404</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -12104,7 +12297,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -12176,7 +12369,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -12248,7 +12441,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -12320,7 +12513,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -12392,7 +12585,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -12464,7 +12657,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -12552,24 +12745,24 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -12583,7 +12776,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -12619,7 +12812,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -12693,7 +12886,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -12743,7 +12936,7 @@
         <v>1512000</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -12815,7 +13008,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -12865,7 +13058,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -12937,7 +13130,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -13009,7 +13202,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -13059,7 +13252,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -13131,7 +13324,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -13203,7 +13396,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -13275,7 +13468,7 @@
         <v>58000</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -13347,7 +13540,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -13419,7 +13612,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -13491,7 +13684,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -13563,7 +13756,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -13635,7 +13828,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -13707,7 +13900,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -13779,7 +13972,7 @@
         <v>345000</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -13851,7 +14044,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -13923,7 +14116,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -13995,7 +14188,7 @@
         <v>89000</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -14067,7 +14260,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -14139,7 +14332,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -14211,7 +14404,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -14283,7 +14476,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -14355,7 +14548,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -14427,7 +14620,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -14515,24 +14708,24 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -14546,7 +14739,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -14582,7 +14775,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -14656,7 +14849,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -14706,7 +14899,7 @@
         <v>1512000</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -14778,7 +14971,7 @@
         <v>157000</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -14828,7 +15021,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -14900,7 +15093,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -14972,7 +15165,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -15022,7 +15215,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -15094,7 +15287,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -15166,7 +15359,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -15238,7 +15431,7 @@
         <v>58000</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -15310,7 +15503,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -15382,7 +15575,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -15454,7 +15647,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -15526,7 +15719,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -15598,7 +15791,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -15670,7 +15863,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -15742,7 +15935,7 @@
         <v>345000</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -15814,7 +16007,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -15886,7 +16079,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -15958,7 +16151,7 @@
         <v>89000</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -16030,7 +16223,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -16102,7 +16295,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -16174,7 +16367,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -16246,7 +16439,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -16318,7 +16511,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -16390,7 +16583,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -16480,16 +16673,16 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
         <v>226</v>
       </c>
@@ -16502,7 +16695,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>229</v>
       </c>
@@ -16516,7 +16709,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>231</v>
       </c>
@@ -16530,7 +16723,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>232</v>
       </c>
@@ -16544,7 +16737,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>233</v>
       </c>
@@ -16558,7 +16751,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>234</v>
       </c>
@@ -16572,7 +16765,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>235</v>
       </c>
@@ -16586,7 +16779,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>236</v>
       </c>
@@ -16600,7 +16793,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>237</v>
       </c>
@@ -16608,7 +16801,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>238</v>
       </c>
@@ -16616,7 +16809,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>240</v>
       </c>
@@ -16624,7 +16817,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>241</v>
       </c>
@@ -16632,7 +16825,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>242</v>
       </c>
@@ -16640,7 +16833,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>243</v>
       </c>
@@ -16648,7 +16841,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>244</v>
       </c>
@@ -16656,7 +16849,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>245</v>
       </c>
@@ -16664,7 +16857,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>246</v>
       </c>
@@ -16672,7 +16865,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>247</v>
       </c>
@@ -16680,7 +16873,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>248</v>
       </c>
@@ -16688,7 +16881,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>249</v>
       </c>
@@ -16696,7 +16889,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>250</v>
       </c>
@@ -16704,7 +16897,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>251</v>
       </c>
@@ -16712,7 +16905,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>252</v>
       </c>
@@ -16720,7 +16913,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>253</v>
       </c>
@@ -16728,7 +16921,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
         <v>254</v>
       </c>
@@ -16736,7 +16929,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="18" t="s">
         <v>255</v>
       </c>
@@ -16772,15 +16965,15 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AI13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="14" width="15.6640625" customWidth="1"/>
-    <col min="15" max="31" width="17.6640625" customWidth="1"/>
+    <col min="1" max="14" width="15.6328125" customWidth="1"/>
+    <col min="15" max="31" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -16802,7 +16995,7 @@
       <c r="M1" s="30"/>
       <c r="N1" s="30"/>
     </row>
-    <row r="2" spans="1:35" ht="30" customHeight="1">
+    <row r="2" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -16906,7 +17099,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>134</v>
       </c>
@@ -17010,7 +17203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>140</v>
       </c>
@@ -17114,7 +17307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>143</v>
       </c>
@@ -17218,7 +17411,7 @@
         <v>0.82257143482415795</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>151</v>
       </c>
@@ -17322,7 +17515,7 @@
         <v>0.90278717999182101</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>159</v>
       </c>
@@ -17426,7 +17619,7 @@
         <v>0.871510171982249</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>172</v>
       </c>
@@ -17530,7 +17723,7 @@
         <v>0.93801012383554405</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>191</v>
       </c>
@@ -17634,7 +17827,7 @@
         <v>0.917643833315406</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>206</v>
       </c>
@@ -17738,7 +17931,7 @@
         <v>0.98283175863099204</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>213</v>
       </c>
@@ -17842,7 +18035,7 @@
         <v>0.970937167625606</v>
       </c>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>219</v>
       </c>
@@ -17946,7 +18139,7 @@
         <v>0.99028099551495297</v>
       </c>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>223</v>
       </c>
@@ -18067,9 +18260,9 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -18082,9 +18275,9 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -18097,9 +18290,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -18112,14 +18305,14 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -18130,7 +18323,7 @@
       </c>
       <c r="E1" s="32"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>6</v>
       </c>
@@ -18147,7 +18340,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>134</v>
       </c>
@@ -18164,7 +18357,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="27" t="s">
         <v>140</v>
       </c>
@@ -18181,7 +18374,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="27" t="s">
         <v>143</v>
       </c>
@@ -18198,7 +18391,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="27" t="s">
         <v>151</v>
       </c>
@@ -18215,7 +18408,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="27" t="s">
         <v>159</v>
       </c>
@@ -18232,7 +18425,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="27" t="s">
         <v>172</v>
       </c>
@@ -18249,7 +18442,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="27" t="s">
         <v>191</v>
       </c>
@@ -18266,7 +18459,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="27" t="s">
         <v>206</v>
       </c>
@@ -18283,7 +18476,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="27" t="s">
         <v>213</v>
       </c>
@@ -18300,7 +18493,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="27" t="s">
         <v>219</v>
       </c>
@@ -18317,7 +18510,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="27" t="s">
         <v>223</v>
       </c>
@@ -18349,16 +18542,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="40.6640625" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" customWidth="1"/>
+    <col min="7" max="7" width="40.6328125" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -18374,7 +18567,7 @@
       </c>
       <c r="H1" s="30"/>
     </row>
-    <row r="2" spans="1:8" ht="25" customHeight="1">
+    <row r="2" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -18416,17 +18609,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="7" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="7" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -18441,7 +18634,7 @@
       <c r="F1" s="30"/>
       <c r="G1" s="30"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -18464,7 +18657,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="23">
+    <row r="3" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -18479,7 +18672,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -18502,7 +18695,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>26</v>
       </c>
@@ -18517,7 +18710,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="23">
+    <row r="6" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -18540,7 +18733,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="34">
+    <row r="7" spans="1:7" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -18563,7 +18756,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>27</v>
       </c>
@@ -18578,7 +18771,7 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="23">
+    <row r="9" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -18601,7 +18794,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="34">
+    <row r="10" spans="1:7" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -18624,7 +18817,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="23">
+    <row r="11" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -18647,7 +18840,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="23">
+    <row r="12" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -18670,7 +18863,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="23">
+    <row r="13" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -18693,7 +18886,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="23">
+    <row r="14" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -18716,7 +18909,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="23">
+    <row r="15" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -18739,7 +18932,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="23">
+    <row r="16" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -18762,7 +18955,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="23">
+    <row r="17" spans="1:7" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
@@ -18785,7 +18978,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
@@ -18808,7 +19001,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="23">
+    <row r="19" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -18831,7 +19024,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="23">
+    <row r="20" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
@@ -18854,7 +19047,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>16</v>
       </c>
@@ -18877,7 +19070,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="23">
+    <row r="22" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -18900,7 +19093,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="23">
+    <row r="23" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -18923,7 +19116,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="23">
+    <row r="24" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>19</v>
       </c>
@@ -18946,7 +19139,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>20</v>
       </c>
@@ -18969,7 +19162,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>21</v>
       </c>
@@ -18992,7 +19185,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="23">
+    <row r="27" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>22</v>
       </c>
@@ -19015,7 +19208,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="23">
+    <row r="28" spans="1:7" ht="22" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>23</v>
       </c>
@@ -19053,24 +19246,24 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -19084,7 +19277,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -19120,7 +19313,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -19194,7 +19387,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -19244,7 +19437,7 @@
         <v>8092.7835051546399</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -19316,7 +19509,7 @@
         <v>8092.7835051546399</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -19366,7 +19559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -19436,7 +19629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -19506,7 +19699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -19556,7 +19749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -19626,7 +19819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -19696,7 +19889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -19766,7 +19959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -19836,7 +20029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -19906,7 +20099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -19976,7 +20169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -20046,7 +20239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -20116,7 +20309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -20186,7 +20379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -20256,7 +20449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -20326,7 +20519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -20396,7 +20589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -20466,7 +20659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -20536,7 +20729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -20606,7 +20799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -20676,7 +20869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -20746,7 +20939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -20816,7 +21009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -20886,7 +21079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -20974,24 +21167,24 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -21005,7 +21198,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -21041,7 +21234,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -21115,7 +21308,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -21165,7 +21358,7 @@
         <v>28054.982817869401</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -21237,7 +21430,7 @@
         <v>28054.982817869401</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -21287,7 +21480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -21357,7 +21550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -21427,7 +21620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -21477,7 +21670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -21547,7 +21740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -21617,7 +21810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -21687,7 +21880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -21757,7 +21950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -21827,7 +22020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -21897,7 +22090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -21967,7 +22160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -22037,7 +22230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -22107,7 +22300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -22177,7 +22370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -22247,7 +22440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -22317,7 +22510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -22387,7 +22580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -22457,7 +22650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -22527,7 +22720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -22597,7 +22790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -22667,7 +22860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -22737,7 +22930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -22807,7 +23000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -22895,24 +23088,24 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -22926,7 +23119,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -22962,7 +23155,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -23036,7 +23229,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -23086,7 +23279,7 @@
         <v>146813.19356549799</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -23158,7 +23351,7 @@
         <v>66360.824742268</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -23208,7 +23401,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -23280,7 +23473,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -23352,7 +23545,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -23402,7 +23595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -23472,7 +23665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -23542,7 +23735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -23614,7 +23807,7 @@
         <v>6913.90728476821</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -23686,7 +23879,7 @@
         <v>2538.4615384615399</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -23756,7 +23949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -23826,7 +24019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -23896,7 +24089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -23966,7 +24159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -24036,7 +24229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -24106,7 +24299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -24176,7 +24369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -24246,7 +24439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -24316,7 +24509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -24386,7 +24579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -24456,7 +24649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -24526,7 +24719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -24596,7 +24789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -24666,7 +24859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -24736,7 +24929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -24824,24 +25017,24 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -24855,7 +25048,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -24891,7 +25084,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -24965,7 +25158,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -25015,7 +25208,7 @@
         <v>294932.96819334599</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -25087,7 +25280,7 @@
         <v>107903.780068729</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -25137,7 +25330,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -25209,7 +25402,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -25281,7 +25474,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -25331,7 +25524,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -25403,7 +25596,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -25475,7 +25668,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -25547,7 +25740,7 @@
         <v>36490.066225165603</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -25619,7 +25812,7 @@
         <v>13397.4358974359</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -25689,7 +25882,7 @@
         <v>940.17094017093996</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -25759,7 +25952,7 @@
         <v>327.86885245901601</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -25829,7 +26022,7 @@
         <v>4873.6462093862801</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -25899,7 +26092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -25969,7 +26162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -26039,7 +26232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -26109,7 +26302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -26179,7 +26372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -26249,7 +26442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -26319,7 +26512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -26389,7 +26582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -26459,7 +26652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -26529,7 +26722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -26599,7 +26792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -26669,7 +26862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -26757,24 +26950,24 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
-    <col min="7" max="11" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="21" width="10.6640625" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" customWidth="1"/>
-    <col min="23" max="24" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="7" max="11" width="10.6328125" customWidth="1"/>
+    <col min="12" max="12" width="13.6328125" customWidth="1"/>
+    <col min="13" max="13" width="6.6328125" customWidth="1"/>
+    <col min="14" max="21" width="10.6328125" customWidth="1"/>
+    <col min="22" max="22" width="8.6328125" customWidth="1"/>
+    <col min="23" max="24" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
@@ -26788,7 +26981,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
@@ -26824,7 +27017,7 @@
       <c r="W3" s="30"/>
       <c r="X3" s="30"/>
     </row>
-    <row r="4" spans="1:24" ht="30" customHeight="1">
+    <row r="4" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -26898,7 +27091,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="23">
+    <row r="5" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -26948,7 +27141,7 @@
         <v>440829.70824007801</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -27020,7 +27213,7 @@
         <v>126247.422680412</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>26</v>
       </c>
@@ -27070,7 +27263,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="23">
+    <row r="8" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -27142,7 +27335,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="34">
+    <row r="9" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -27214,7 +27407,7 @@
         <v>56000</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>27</v>
       </c>
@@ -27264,7 +27457,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="23">
+    <row r="11" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -27336,7 +27529,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="34">
+    <row r="12" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -27408,7 +27601,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="23">
+    <row r="13" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -27480,7 +27673,7 @@
         <v>49549.668874172203</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="23">
+    <row r="14" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -27552,7 +27745,7 @@
         <v>18192.307692307699</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="23">
+    <row r="15" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -27624,7 +27817,7 @@
         <v>16923.0769230769</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="23">
+    <row r="16" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -27696,7 +27889,7 @@
         <v>5901.6393442623003</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="23">
+    <row r="17" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -27768,7 +27961,7 @@
         <v>32490.974729241902</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="23">
+    <row r="18" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -27838,7 +28031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="23">
+    <row r="19" spans="1:24" ht="32.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -27908,7 +28101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -27980,7 +28173,7 @@
         <v>53419.354838709703</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="23">
+    <row r="21" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -28052,7 +28245,7 @@
         <v>7105.2631578947403</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="23">
+    <row r="22" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -28124,7 +28317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -28194,7 +28387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="23">
+    <row r="24" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -28264,7 +28457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="23">
+    <row r="25" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -28334,7 +28527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="23">
+    <row r="26" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -28404,7 +28597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -28474,7 +28667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -28544,7 +28737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="23">
+    <row r="29" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -28614,7 +28807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="23">
+    <row r="30" spans="1:24" ht="22" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>23</v>
       </c>
